--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/2718-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/2718-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1349A7FB-5970-4D45-BFCA-1DCE56688BC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E175AF14-63F8-4880-97B4-68F9042E6995}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{F6463D2B-3FE9-4749-9D2D-FDC1E7E1717F}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{BA66C6F3-BAE0-44F4-A97B-37EE51A38519}"/>
   </bookViews>
   <sheets>
     <sheet name="2718-dividend-20260225_0_4" sheetId="1" r:id="rId1"/>
@@ -1439,25 +1439,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B9FB344-6264-41D4-A110-8BCDC47EC163}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7AB6D65F-B3B4-45DB-8EB0-652835D82745}">
   <dimension ref="A1:R29"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="2" width="7.33203125" customWidth="1"/>
-    <col min="3" max="3" width="8.6640625" customWidth="1"/>
-    <col min="4" max="4" width="8.33203125" customWidth="1"/>
-    <col min="5" max="5" width="8" customWidth="1"/>
-    <col min="6" max="6" width="8.33203125" customWidth="1"/>
-    <col min="7" max="9" width="8" customWidth="1"/>
-    <col min="10" max="10" width="8.33203125" customWidth="1"/>
-    <col min="11" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="8.33203125" customWidth="1"/>
-    <col min="15" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="8.88671875" customWidth="1"/>
+    <col min="1" max="1" width="6.5" customWidth="1"/>
+    <col min="2" max="2" width="9.25" customWidth="1"/>
+    <col min="3" max="3" width="10.75" customWidth="1"/>
+    <col min="4" max="4" width="10.5" customWidth="1"/>
+    <col min="5" max="5" width="10" customWidth="1"/>
+    <col min="6" max="6" width="10.5" customWidth="1"/>
+    <col min="7" max="9" width="10" customWidth="1"/>
+    <col min="10" max="10" width="10.5" customWidth="1"/>
+    <col min="11" max="13" width="10" customWidth="1"/>
+    <col min="14" max="14" width="10.5" customWidth="1"/>
+    <col min="15" max="17" width="10" customWidth="1"/>
+    <col min="18" max="18" width="10.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
@@ -1485,7 +1485,7 @@
       <c r="Q1" s="30"/>
       <c r="R1" s="22"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="23" t="s">
         <v>1</v>
       </c>
@@ -1515,7 +1515,7 @@
       <c r="Q2" s="32"/>
       <c r="R2" s="33"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="23" t="s">
         <v>2</v>
       </c>
@@ -1561,7 +1561,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="25"/>
       <c r="B4" s="26"/>
       <c r="C4" s="7"/>
@@ -1611,7 +1611,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="37">
         <v>2026</v>
       </c>
@@ -1665,7 +1665,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
         <v>26</v>
       </c>
@@ -1721,7 +1721,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="39">
         <v>2025</v>
       </c>
@@ -1775,7 +1775,7 @@
         <v>7.72</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="17" t="s">
         <v>26</v>
       </c>
@@ -1831,7 +1831,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="17" t="s">
         <v>26</v>
       </c>
@@ -1887,7 +1887,7 @@
         <v>2.62</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="17" t="s">
         <v>26</v>
       </c>
@@ -1943,7 +1943,7 @@
         <v>5.0999999999999996</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="37">
         <v>2024</v>
       </c>
@@ -1997,7 +1997,7 @@
         <v>2.54</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="39">
         <v>2023</v>
       </c>
@@ -2051,7 +2051,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="37">
         <v>2022</v>
       </c>
@@ -2105,7 +2105,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="39">
         <v>2021</v>
       </c>
@@ -2159,7 +2159,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="37">
         <v>2020</v>
       </c>
@@ -2213,7 +2213,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="39">
         <v>2019</v>
       </c>
@@ -2267,7 +2267,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="37">
         <v>2018</v>
       </c>
@@ -2321,7 +2321,7 @@
         <v>0.95</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="39">
         <v>2017</v>
       </c>
@@ -2375,7 +2375,7 @@
         <v>2.0299999999999998</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="37">
         <v>2016</v>
       </c>
@@ -2429,7 +2429,7 @@
         <v>2.64</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="39">
         <v>2015</v>
       </c>
@@ -2483,7 +2483,7 @@
         <v>1.54</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="37">
         <v>2014</v>
       </c>
@@ -2537,7 +2537,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="39">
         <v>2013</v>
       </c>
@@ -2591,7 +2591,7 @@
         <v>2.13</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="37">
         <v>2012</v>
       </c>
@@ -2645,7 +2645,7 @@
         <v>3.3</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="39">
         <v>2011</v>
       </c>
@@ -2699,7 +2699,7 @@
         <v>2.4300000000000002</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="37">
         <v>2010</v>
       </c>
@@ -2753,7 +2753,7 @@
         <v>1.97</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="39">
         <v>2009</v>
       </c>
@@ -2807,7 +2807,7 @@
         <v>3.66</v>
       </c>
     </row>
-    <row r="27" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="37">
         <v>2008</v>
       </c>
@@ -2861,7 +2861,7 @@
         <v>3.97</v>
       </c>
     </row>
-    <row r="28" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="39">
         <v>2007</v>
       </c>
@@ -2915,7 +2915,7 @@
         <v>6.69</v>
       </c>
     </row>
-    <row r="29" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="37" t="s">
         <v>32</v>
       </c>
